--- a/C/14. TESTING & QUALITY ASSURANCE.xlsx
+++ b/C/14. TESTING & QUALITY ASSURANCE.xlsx
@@ -5,14 +5,16 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document\02.Study\Linux\Kỹ Thuật lập trình\C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document\02.Study\Programming Techniques\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8490" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Crash hệ thống là gì " sheetId="3" r:id="rId1"/>
+    <sheet name="Top Lỗi phổ biến" sheetId="1" r:id="rId2"/>
+    <sheet name="Ảnh hưởng" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,9 +25,1374 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="279">
+  <si>
+    <t>I. LỖI LIÊN QUAN ĐẾN ĐỒNG THỜI (Concurrency)</t>
+  </si>
+  <si>
+    <t>Định nghĩa</t>
+  </si>
+  <si>
+    <t>Đặc điểm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xảy ra khi nhiều luồng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cùng thao tác lên tài nguyên chung</t>
+    </r>
+  </si>
+  <si>
+    <t>Không được kiểm soát thứ tự</t>
+  </si>
+  <si>
+    <t>Ví dụ</t>
+  </si>
+  <si>
+    <t>x = x + 1;   // thread A</t>
+  </si>
+  <si>
+    <t>x = x + 1;   // thread B</t>
+  </si>
+  <si>
+    <t>➡️ Kết quả có thể là 1 hoặc 2</t>
+  </si>
+  <si>
+    <t>Định nghĩa (chuẩn C/C++)</t>
+  </si>
+  <si>
+    <t>Hệ quả</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❗ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Undefined Behavior</t>
+    </r>
+  </si>
+  <si>
+    <t>Compiler có quyền tối ưu phá nát chương trình</t>
+  </si>
+  <si>
+    <t>int x;</t>
+  </si>
+  <si>
+    <t>Thread A: x = 1;</t>
+  </si>
+  <si>
+    <t>Thread B: printf("%d", x);</t>
+  </si>
+  <si>
+    <t>Điều kiện (4 điều kiện Coffman)</t>
+  </si>
+  <si>
+    <t>1. Mutual exclusion</t>
+  </si>
+  <si>
+    <t>2. Hold and wait</t>
+  </si>
+  <si>
+    <t>3. No preemption</t>
+  </si>
+  <si>
+    <t>4. Circular wait</t>
+  </si>
+  <si>
+    <t>Thread A: lock(m1) → wait m2</t>
+  </si>
+  <si>
+    <t>Thread B: lock(m2) → wait m1</t>
+  </si>
+  <si>
+    <t>II. LỖI BỘ NHỚ (Memory Errors)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Truy cập bộ nhớ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đã free</t>
+    </r>
+  </si>
+  <si>
+    <t>free(p);</t>
+  </si>
+  <si>
+    <t>*p = 10;   // ❌</t>
+  </si>
+  <si>
+    <t>➡️ Có thể crash hoặc bị exploit</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giải phóng cùng một vùng nhớ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 lần</t>
+    </r>
+  </si>
+  <si>
+    <t>free(p);   // ❌</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cấp phát nhưng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không bao giờ free</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Con trỏ trỏ tới vùng nhớ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không còn hợp lệ</t>
+    </r>
+  </si>
+  <si>
+    <t>int* p = malloc(...);</t>
+  </si>
+  <si>
+    <t>Ghi vượt quá kích thước vùng nhớ cấp phát</t>
+  </si>
+  <si>
+    <t>char buf[8];</t>
+  </si>
+  <si>
+    <t>strcpy(buf, "123456789"); // ❌</t>
+  </si>
+  <si>
+    <t>III. LỖI LOGIC &amp; THIẾT KẾ</t>
+  </si>
+  <si>
+    <t>Ví dụ UB</t>
+  </si>
+  <si>
+    <t>Data race</t>
+  </si>
+  <si>
+    <t>Dereference NULL</t>
+  </si>
+  <si>
+    <t>Signed integer overflow</t>
+  </si>
+  <si>
+    <t>Shift quá số bit</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng biến </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chưa được gán giá trị</t>
+    </r>
+  </si>
+  <si>
+    <t>printf("%d", x); // ❌</t>
+  </si>
+  <si>
+    <t>Tràn số (đặc biệt nguy hiểm với signed int)</t>
+  </si>
+  <si>
+    <t>int x = INT_MAX + 1; // UB</t>
+  </si>
+  <si>
+    <t>Ép kiểu sai, dùng object không đúng type thực</t>
+  </si>
+  <si>
+    <t>Base* b = (Base*)derived;</t>
+  </si>
+  <si>
+    <t>IV. LỖI API / HỆ THỐNG</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kiểm tra xong nhưng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dữ liệu thay đổi trước khi dùng</t>
+    </r>
+  </si>
+  <si>
+    <t>if (file_exists(path))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    open(path); // path có thể bị đổi</t>
+  </si>
+  <si>
+    <t>Không giải phóng:</t>
+  </si>
+  <si>
+    <t>File descriptor</t>
+  </si>
+  <si>
+    <t>Mutex</t>
+  </si>
+  <si>
+    <t>Socket</t>
+  </si>
+  <si>
+    <t>V. LỖI C/C++ ĐẶC TRƯNG</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gán object con cho biến cha </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bằng giá trị</t>
+    </r>
+  </si>
+  <si>
+    <t>Shape s = Circle(); // mất phần Circle</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Delete object con qua con trỏ cha </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không có destructor virtual</t>
+    </r>
+  </si>
+  <si>
+    <t>Shape* s = new Circle();</t>
+  </si>
+  <si>
+    <t>delete s; // UB nếu ~Shape không virtual</t>
+  </si>
+  <si>
+    <t>Struct layout khác nhau giữa compiler / platform</t>
+  </si>
+  <si>
+    <t>📌 Rất nguy hiểm trong embedded / IPC</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kết quả chương trình </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>phụ thuộc vào thứ tự thực thi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của các thread/process.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hai hoặc nhiều thread </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>truy cập cùng một vùng nhớ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ít nhất một là ghi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>không có đồng bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Các thread </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chờ nhau vĩnh viễn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, không thread nào tiếp tục.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thread </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không bị block</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, nhưng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>liên tục nhường nhau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, không tiến triển.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Một thread </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không bao giờ được cấp tài nguyên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do thread khác chiếm mãi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hành vi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không được tiêu chuẩn định nghĩa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, compiler muốn làm gì thì làm.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Race Condition</t>
+  </si>
+  <si>
+    <t>2. Data Race (nghiêm trọng hơn)</t>
+  </si>
+  <si>
+    <t>Race condition là khái niệm logic, mức cao.</t>
+  </si>
+  <si>
+    <t>Data race ⊂ Race condition</t>
+  </si>
+  <si>
+    <t>Mọi data race đều nguy hiểm</t>
+  </si>
+  <si>
+    <t>3. Deadlock</t>
+  </si>
+  <si>
+    <t>4. Livelock</t>
+  </si>
+  <si>
+    <t>CPU chạy 100% nhưng không làm xong việc</t>
+  </si>
+  <si>
+    <t>5. Starvation</t>
+  </si>
+  <si>
+    <t>6. Use After Free (UAF)</t>
+  </si>
+  <si>
+    <t>7. Double Free</t>
+  </si>
+  <si>
+    <t>8. Memory Leak</t>
+  </si>
+  <si>
+    <t>Đặc biệt nguy hiểm trong embedded / service dài hạn</t>
+  </si>
+  <si>
+    <t>10. Buffer Overflow</t>
+  </si>
+  <si>
+    <t>9. Dangling Pointer</t>
+  </si>
+  <si>
+    <t>11. Undefined Behavior (UB)</t>
+  </si>
+  <si>
+    <t>UB ≠ crash ngay</t>
+  </si>
+  <si>
+    <t>12. Uninitialized Variable</t>
+  </si>
+  <si>
+    <t>13. Integer Overflow / Underflow</t>
+  </si>
+  <si>
+    <t>14. Type Confusion</t>
+  </si>
+  <si>
+    <t>Dễ gặp khi tự viết vtable trong C</t>
+  </si>
+  <si>
+    <t>15.TOCTOU (Time Of Check – Time Of Use)</t>
+  </si>
+  <si>
+    <t>16. Resource Leak</t>
+  </si>
+  <si>
+    <t>19. ABI / Alignment Issues</t>
+  </si>
+  <si>
+    <t>18. Missing Virtual Destructor (C++)</t>
+  </si>
+  <si>
+    <t>17. Object Slicing (C++)</t>
+  </si>
+  <si>
+    <t>Ảnh hưởng đến hệ thống</t>
+  </si>
+  <si>
+    <t>Phụ thuộc scheduler / timing / CPU load</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Debug bằng log thường </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>làm mất bug</t>
+    </r>
+  </si>
+  <si>
+    <t>Giá trị cảm biến sai</t>
+  </si>
+  <si>
+    <t>State machine nhảy trạng thái bất thường</t>
+  </si>
+  <si>
+    <t>reorder</t>
+  </si>
+  <si>
+    <t>cache register</t>
+  </si>
+  <si>
+    <t>bỏ hẳn đoạn code</t>
+  </si>
+  <si>
+    <t>chạy sai</t>
+  </si>
+  <si>
+    <t>crash</t>
+  </si>
+  <si>
+    <t>chạy “đúng giả tạo”</t>
+  </si>
+  <si>
+    <t>Không thể suy luận bằng logic người</t>
+  </si>
+  <si>
+    <t>Code đúng → compiler phá</t>
+  </si>
+  <si>
+    <t>ISR + main cùng truy cập biến → lỗi ngẫu nhiên</t>
+  </si>
+  <si>
+    <t>Thanh ghi peripheral bị đọc sai</t>
+  </si>
+  <si>
+    <t>CPU thấp</t>
+  </si>
+  <si>
+    <t>Không tiến triển</t>
+  </si>
+  <si>
+    <t>Tài nguyên bị khóa mãi</t>
+  </si>
+  <si>
+    <t>Task RTOS bị treo</t>
+  </si>
+  <si>
+    <t>Mất realtime guarantee</t>
+  </si>
+  <si>
+    <t>Thread vẫn chạy</t>
+  </si>
+  <si>
+    <t>Nhưng không tiến triển</t>
+  </si>
+  <si>
+    <t>Task ưu tiên cao chiếm CPU</t>
+  </si>
+  <si>
+    <t>Task quan trọng không chạy</t>
+  </si>
+  <si>
+    <t>Task ưu tiên thấp không bao giờ được schedule</t>
+  </si>
+  <si>
+    <t>Watchdog reset</t>
+  </si>
+  <si>
+    <t>Ảnh hưởng</t>
+  </si>
+  <si>
+    <t>Remote Code Execution</t>
+  </si>
+  <si>
+    <t>Privilege Escalation</t>
+  </si>
+  <si>
+    <t>Corrupt heap → reset MCU</t>
+  </si>
+  <si>
+    <t>Hỏng control block RTOS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lỗi xuất hiện </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xa vị trí bug</t>
+    </r>
+  </si>
+  <si>
+    <t>Cực kỳ nguy hiểm</t>
+  </si>
+  <si>
+    <t>Không có swap</t>
+  </si>
+  <si>
+    <t>Hệ thống chết sau vài giờ/ngày</t>
+  </si>
+  <si>
+    <t>Truyền con trỏ qua module</t>
+  </si>
+  <si>
+    <t>Callback / ISR</t>
+  </si>
+  <si>
+    <t>Stack smashing</t>
+  </si>
+  <si>
+    <t>ROP</t>
+  </si>
+  <si>
+    <t>Ghi đè return address → hard fault</t>
+  </si>
+  <si>
+    <t>UB ≠ crash</t>
+  </si>
+  <si>
+    <t>UB = mất quyền suy luận</t>
+  </si>
+  <si>
+    <t>Thanh ghi chưa reset</t>
+  </si>
+  <si>
+    <t>Giá trị ADC giả</t>
+  </si>
+  <si>
+    <t>UB → compiler phá</t>
+  </si>
+  <si>
+    <t>Counter tràn → timer sai</t>
+  </si>
+  <si>
+    <t>Sai offset → gọi nhầm function pointer</t>
+  </si>
+  <si>
+    <t>Check file → attacker đổi symlink</t>
+  </si>
+  <si>
+    <t>Ít gặp hơn nhưng vẫn có (shared config)</t>
+  </si>
+  <si>
+    <t>Mutex không release → deadlock gián tiếp</t>
+  </si>
+  <si>
+    <t>bộ nhớ</t>
+  </si>
+  <si>
+    <t>quyền truy cập</t>
+  </si>
+  <si>
+    <t>tính toàn vẹn trạng thái</t>
+  </si>
+  <si>
+    <t>Bug logic → chạy sai</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crash → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không chạy được nữa</t>
+    </r>
+  </si>
+  <si>
+    <t>A. Crash chương trình (User-space, PC / Linux / Windows)</t>
+  </si>
+  <si>
+    <t>Điều gì xảy ra?</t>
+  </si>
+  <si>
+    <t>Giải phóng tài nguyên</t>
+  </si>
+  <si>
+    <t>Các chương trình khác vẫn chạy</t>
+  </si>
+  <si>
+    <t>Ví dụ nguyên nhân</t>
+  </si>
+  <si>
+    <t>Segmentation fault (SIGSEGV)</t>
+  </si>
+  <si>
+    <t>Illegal instruction (SIGILL)</t>
+  </si>
+  <si>
+    <t>Stack overflow</t>
+  </si>
+  <si>
+    <t>Abort()</t>
+  </si>
+  <si>
+    <t>int* p = NULL;</t>
+  </si>
+  <si>
+    <t>*p = 10;   // crash</t>
+  </si>
+  <si>
+    <t>Chương trình tự thoát</t>
+  </si>
+  <si>
+    <t>Có core dump</t>
+  </si>
+  <si>
+    <t>Log lỗi</t>
+  </si>
+  <si>
+    <t>B. Crash hệ thống (Kernel / OS level)</t>
+  </si>
+  <si>
+    <t>Kernel gặp lỗi nghiêm trọng</t>
+  </si>
+  <si>
+    <t>Toàn bộ hệ thống dừng</t>
+  </si>
+  <si>
+    <t>Phải reboot</t>
+  </si>
+  <si>
+    <t>Kernel panic (Linux)</t>
+  </si>
+  <si>
+    <t>Blue Screen of Death (Windows)</t>
+  </si>
+  <si>
+    <t>Driver lỗi</t>
+  </si>
+  <si>
+    <t>Ghi nhầm kernel memory</t>
+  </si>
+  <si>
+    <t>Race trong kernel</t>
+  </si>
+  <si>
+    <t>C. Crash trong Embedded / MCU (quan trọng với bạn)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCU </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HardFault / BusFault / UsageFault</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CPU </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhảy vào fault handler</t>
+    </r>
+  </si>
+  <si>
+    <t>Thường dẫn đến:</t>
+  </si>
+  <si>
+    <t>reset</t>
+  </si>
+  <si>
+    <t>treo vĩnh viễn</t>
+  </si>
+  <si>
+    <t>watchdog reset</t>
+  </si>
+  <si>
+    <t>Các dạng crash phổ biến</t>
+  </si>
+  <si>
+    <t>1. Crash ngay lập tức</t>
+  </si>
+  <si>
+    <t>Truy cập bộ nhớ sai</t>
+  </si>
+  <si>
+    <t>Jump vào địa chỉ rác</t>
+  </si>
+  <si>
+    <t>➡️ MCU reset / app chết</t>
+  </si>
+  <si>
+    <t>2. Crash trễ (Delayed crash)</t>
+  </si>
+  <si>
+    <t>Heap corruption</t>
+  </si>
+  <si>
+    <t>Stack overwrite</t>
+  </si>
+  <si>
+    <t>3. Silent crash (nguy hiểm nhất)</t>
+  </si>
+  <si>
+    <t>Không reset</t>
+  </si>
+  <si>
+    <t>Nhưng:</t>
+  </si>
+  <si>
+    <t>logic hỏng</t>
+  </si>
+  <si>
+    <t>dữ liệu sai</t>
+  </si>
+  <si>
+    <t>hệ thống treo ngầm</t>
+  </si>
+  <si>
+    <t>Crash</t>
+  </si>
+  <si>
+    <t>Treo</t>
+  </si>
+  <si>
+    <t>Dừng hẳn</t>
+  </si>
+  <si>
+    <t>CPU vẫn chạy</t>
+  </si>
+  <si>
+    <t>Reset / kill</t>
+  </si>
+  <si>
+    <t>Không phản hồi</t>
+  </si>
+  <si>
+    <t>Dễ phát hiện</t>
+  </si>
+  <si>
+    <t>Khó debug</t>
+  </si>
+  <si>
+    <t>1. “Crash hệ thống” là gì? (định nghĩa ngắn gọn)</t>
+  </si>
+  <si>
+    <t>2. Crash ở các mức khác nhau</t>
+  </si>
+  <si>
+    <t>Biểu hiện:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OS </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giết tiến trình</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Crash khác gì với Treo (Hang)?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Watchdog xử lý treo, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không xử lý crash logic</t>
+    </r>
+  </si>
+  <si>
+    <t>Embedded rất hay gặp</t>
+  </si>
+  <si>
+    <t>3. Crash KHÔNG phải lúc nào cũng “dừng ngay”</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lỗi xảy ra ở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, crash ở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Crash hệ thống</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là trạng thái mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chương trình hoặc toàn bộ hệ thống không thể tiếp tục thực thi đúng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bị dừng đột ngột hoặc buộc phải reset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, do vi phạm nghiêm trọng về:</t>
+    </r>
+  </si>
+  <si>
+    <t>Crash ≠ bug logic</t>
+  </si>
+  <si>
+    <t>15. TOCTOU</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kết quả không xác định theo thời gian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Undefined Behavior (theo chuẩn C/C++)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hệ thống đứng vĩnh viễn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CPU chạy 100% nhưng không làm việc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Một phần hệ thống không bao giờ hoạt động</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bug khó tái hiện (Heisenbug)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compiler có quyền:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không crash → watchdog mới phát hiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pin / năng lượng tiêu hao mạnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vi phạm fairness</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test pass, production fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dịch vụ treo, không phản hồi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Realtime bị phá</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Realtime task bị trễ vô hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logic sai nhưng không crash</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hệ thống có thể:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Crash ngẫu nhiên</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heap corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tăng RAM dần theo thời gian</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Truy cập rác</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ghi đè stack / heap</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ghi đè dữ liệu khác</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Crash ở lần malloc/free sau</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chậm → treo → crash</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Crash</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lỗ hổng bảo mật cực nặng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security exploit (heap metadata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UAF trá hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lỗ hổng bảo mật kinh điển</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không thể dự đoán</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Giá trị rác</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logic sai</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gọi nhầm hàm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compiler hợp pháp phá code</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logic sai ngẫu nhiên</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Loop vô hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Đọc sai layout bộ nhớ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không portable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phụ thuộc stack layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bypass check bảo mật</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Crash / UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lỗ hổng bảo mật</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cạn tài nguyên hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Race với filesystem / resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không tạo được thread/socket mới</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Treo toàn hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Biểu hiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Khác deadlock:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Embedded:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Đặc trưng hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trong embedded:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tác động nặng nhất</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Security:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Debug:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Đặc biệt nguy hiểm khi:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quan trọng:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Signed overflow:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tự viết vtable trong C:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ví dụ:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không có OS để “cứu”</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nguyên nhân:</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -34,16 +1401,71 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -51,12 +1473,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,9 +1848,1711 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:AW43"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:49" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+    </row>
+    <row r="3" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="B4" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="B5" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="B6" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:49" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="T13" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AH13" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI13" s="21"/>
+      <c r="AJ13" s="21"/>
+      <c r="AK13" s="21"/>
+      <c r="AL13" s="21"/>
+      <c r="AM13" s="21"/>
+      <c r="AN13" s="21"/>
+      <c r="AO13" s="21"/>
+      <c r="AP13" s="21"/>
+      <c r="AQ13" s="21"/>
+      <c r="AR13" s="21"/>
+      <c r="AS13" s="21"/>
+      <c r="AT13" s="21"/>
+      <c r="AU13" s="21"/>
+      <c r="AV13" s="21"/>
+      <c r="AW13" s="21"/>
+    </row>
+    <row r="14" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH14" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="T15" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="T16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH16" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="T17" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH17" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI17" s="11"/>
+      <c r="AJ17" s="11"/>
+      <c r="AK17" s="11"/>
+    </row>
+    <row r="18" spans="1:37" ht="15" x14ac:dyDescent="0.25">
+      <c r="AH18" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI18" s="11"/>
+      <c r="AJ18" s="11"/>
+      <c r="AK18" s="11"/>
+    </row>
+    <row r="19" spans="1:37" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH19" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI19" s="11"/>
+      <c r="AJ19" s="11"/>
+      <c r="AK19" s="11"/>
+    </row>
+    <row r="20" spans="1:37" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH20" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="AI20" s="11"/>
+      <c r="AJ20" s="11"/>
+      <c r="AK20" s="11"/>
+    </row>
+    <row r="21" spans="1:37" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="AI21" s="11"/>
+      <c r="AJ21" s="11"/>
+      <c r="AK21" s="11"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="T24" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:32" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="W34" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="X35" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+      <c r="AF35" s="17"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="M36" s="19"/>
+      <c r="X36" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y36" s="18"/>
+      <c r="Z36" s="18"/>
+      <c r="AA36" s="18"/>
+      <c r="AB36" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
+      <c r="AF36" s="18"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="X37" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y37" s="18"/>
+      <c r="Z37" s="18"/>
+      <c r="AA37" s="18"/>
+      <c r="AB37" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="18"/>
+      <c r="AE37" s="18"/>
+      <c r="AF37" s="18"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="X38" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+    </row>
+    <row r="39" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+      <c r="M39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="W39" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="X35:AA35"/>
+    <mergeCell ref="X36:AA36"/>
+    <mergeCell ref="X37:AA37"/>
+    <mergeCell ref="X38:AA38"/>
+    <mergeCell ref="AB35:AF35"/>
+    <mergeCell ref="AB36:AF36"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="AB38:AF38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BK51"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:63" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="Y2" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AP2" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="21"/>
+      <c r="BH2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="BI2" s="21"/>
+      <c r="BJ2" s="21"/>
+      <c r="BK2" s="21"/>
+    </row>
+    <row r="3" spans="1:63" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH4" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63" ht="15" x14ac:dyDescent="0.2">
+      <c r="Y5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH5" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:63" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="BH7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BH8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63" ht="15" x14ac:dyDescent="0.2">
+      <c r="Y9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="BH9" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:63" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP10" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:63" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="Y13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP13" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP14" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y15" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="Y16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="Y17" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:61" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="M20" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="Y20" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="21"/>
+      <c r="AC20" s="21"/>
+      <c r="AO20" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP20" s="21"/>
+      <c r="AQ20" s="21"/>
+      <c r="AR20" s="21"/>
+      <c r="AS20" s="21"/>
+      <c r="AT20" s="21"/>
+      <c r="BD20" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="BE20" s="21"/>
+      <c r="BF20" s="21"/>
+      <c r="BG20" s="21"/>
+      <c r="BH20" s="21"/>
+      <c r="BI20" s="21"/>
+    </row>
+    <row r="21" spans="1:61" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="BD22" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BD24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:61" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="X28" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="21"/>
+      <c r="AE28" s="21"/>
+      <c r="AK28" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL28" s="21"/>
+      <c r="AM28" s="21"/>
+      <c r="AN28" s="21"/>
+      <c r="AO28" s="21"/>
+      <c r="AP28" s="21"/>
+      <c r="AQ28" s="21"/>
+      <c r="AR28" s="21"/>
+      <c r="AS28" s="21"/>
+      <c r="AT28" s="21"/>
+      <c r="AY28" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ28" s="21"/>
+      <c r="BA28" s="21"/>
+      <c r="BB28" s="21"/>
+      <c r="BC28" s="21"/>
+      <c r="BD28" s="21"/>
+    </row>
+    <row r="29" spans="1:61" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY29" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY30" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK31" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY32" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY33" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:51" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="T39" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="U39" s="21"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="21"/>
+      <c r="X39" s="21"/>
+      <c r="Y39" s="21"/>
+    </row>
+    <row r="40" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="T42" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T44" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:51" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI47" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:51" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI48" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI49" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI50" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="O51" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BM60"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:65" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="Q2" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AH2" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="21"/>
+      <c r="AV2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW2" s="21"/>
+      <c r="AX2" s="21"/>
+      <c r="AY2" s="21"/>
+      <c r="BJ2" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK2" s="21"/>
+      <c r="BL2" s="21"/>
+      <c r="BM2" s="21"/>
+    </row>
+    <row r="3" spans="1:65" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ3" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="Q4" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="AV4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="BJ4" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="Q5" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AV5" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ5" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="Q6" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AV6" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ6" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="Q7" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="Q8" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="BJ8" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ9" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="BJ10" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:65" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH11" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="Q12" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV12" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="AH13" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV13" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:65" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="AH14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV14" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="Q16" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Q19" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Q20" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:52" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="N23" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="Y23" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AJ23" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK23" s="21"/>
+      <c r="AL23" s="21"/>
+      <c r="AM23" s="21"/>
+      <c r="AN23" s="21"/>
+      <c r="AO23" s="21"/>
+      <c r="AU23" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV23" s="21"/>
+      <c r="AW23" s="21"/>
+      <c r="AX23" s="21"/>
+      <c r="AY23" s="21"/>
+      <c r="AZ23" s="21"/>
+    </row>
+    <row r="24" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU24" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A25" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AJ25" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="AU25" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="AV25" s="10"/>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y26" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="AJ26" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="AU26" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="AV26" s="10"/>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="AJ27" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="AU27" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV27" s="10"/>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="AU29" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y30" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU30" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ31" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU31" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AU33" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AU34" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:47" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:47" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="M38" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="21"/>
+      <c r="W38" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="X38" s="21"/>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="21"/>
+      <c r="AA38" s="21"/>
+      <c r="AB38" s="21"/>
+      <c r="AC38" s="21"/>
+      <c r="AD38" s="21"/>
+      <c r="AE38" s="21"/>
+      <c r="AF38" s="21"/>
+      <c r="AJ38" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK38" s="21"/>
+      <c r="AL38" s="21"/>
+      <c r="AM38" s="21"/>
+      <c r="AN38" s="21"/>
+      <c r="AO38" s="21"/>
+    </row>
+    <row r="39" spans="1:47" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="W39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ39" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A40" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="M40" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="W40" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ40" s="13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="M41" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="W41" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AJ41" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="10"/>
+      <c r="M42" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="W42" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ42" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AJ44" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ45" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="W48" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:19" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="N51" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="21"/>
+      <c r="S51" s="21"/>
+    </row>
+    <row r="52" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="N53" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A54" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="N54" s="13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="N55" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="N58" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>